--- a/washout-logP-relation/Potentiator_table_v1.2.xlsx
+++ b/washout-logP-relation/Potentiator_table_v1.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanborowsky/Documents/grabelab/projects/cftr-glpg/cftr-potentiator-SAR/washout-logP-relation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35DB308A-B703-7B4D-8E37-0D92889A6956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51D2414E-2407-D04E-A417-B34026B662D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{57DC9696-787F-1B4F-B4AE-CFB6C52D21EC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="60">
   <si>
     <t>Molecule name</t>
   </si>
@@ -214,6 +214,9 @@
   <si>
     <t>computed with https://vcclab.org/web/alogps/ Tetko, I. V.; Gasteiger, J.; Todeschini, R.; Mauri, A.; Livingstone, D.; Ertl, P.; Palyulin, V. A.; Radchenko, E. V.; Zefirov, N. S.; Makarenko, A. S.; Tanchuk, V. Y.; Prokopenko, V. V. Virtual computational chemistry laboratory - design and description, J. Comput. Aid. Mol. Des., 2005, 19, 453-63, article.
 VCCLAB, Virtual Computational Chemistry Laboratory, https://vcclab.org, 2005.</t>
+  </si>
+  <si>
+    <t>Rowan says only the neutral form is relevant at physiological pH</t>
   </si>
 </sst>
 </file>
@@ -325,7 +328,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -376,7 +379,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1764,7 +1766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C92C17B-6CCF-2140-B9FE-FB98CAC50E36}">
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -1784,7 +1786,7 @@
     <col min="17" max="17" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C1" s="21" t="s">
         <v>34</v>
       </c>
@@ -1796,11 +1798,11 @@
       <c r="J1" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="24" t="s">
+      <c r="K1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="2" customFormat="1" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" s="2" customFormat="1" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1850,7 +1852,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="49" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="15" t="s">
         <v>21</v>
       </c>
@@ -1903,7 +1905,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
@@ -1952,8 +1954,11 @@
       <c r="Q4" s="1">
         <v>2.06</v>
       </c>
+      <c r="R4" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="5" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="5" t="s">
         <v>13</v>
       </c>
@@ -2003,7 +2008,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="5" t="s">
         <v>2</v>
       </c>
@@ -2053,7 +2058,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="5" t="s">
         <v>3</v>
       </c>
@@ -2103,7 +2108,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="5" t="s">
         <v>4</v>
       </c>
